--- a/test.xlsx
+++ b/test.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,11 @@
           <t>mt</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -447,6 +452,11 @@
           <t>机器翻译质里</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>机器翻译质量</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -454,27 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>completely same</t>
+          <t>hello world</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>completely same</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>apple banana</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>aple banana</t>
+          <t>hello word</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>hello world</t>
         </is>
       </c>
     </row>
